--- a/artfynd/A 28811-2022 artfynd.xlsx
+++ b/artfynd/A 28811-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 28811-2022 artfynd.xlsx
+++ b/artfynd/A 28811-2022 artfynd.xlsx
@@ -2989,10 +2989,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119738082</v>
+        <v>119738933</v>
       </c>
       <c r="B22" t="n">
-        <v>78262</v>
+        <v>91840</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3001,25 +3001,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3029,10 +3029,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>417270</v>
+        <v>417238</v>
       </c>
       <c r="R22" t="n">
-        <v>6900698</v>
+        <v>6900663</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3074,7 +3074,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3089,22 +3089,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Liam Martin</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Liam Martin, Alexander Hoffmann</t>
+          <t>Alexander Hoffmann, Liam Martin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119738482</v>
+        <v>119738721</v>
       </c>
       <c r="B23" t="n">
-        <v>57421</v>
+        <v>78262</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3113,47 +3113,28 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103031</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Flobäcken, Flobäcken, Hjd</t>
@@ -3195,7 +3176,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3205,7 +3186,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3232,10 +3213,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119739081</v>
+        <v>119738011</v>
       </c>
       <c r="B24" t="n">
-        <v>78262</v>
+        <v>79115</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3248,21 +3229,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3278,7 +3259,7 @@
         <v>6900663</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3307,7 +3288,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3317,7 +3298,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3344,10 +3325,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119738266</v>
+        <v>119739014</v>
       </c>
       <c r="B25" t="n">
-        <v>79115</v>
+        <v>91840</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3356,37 +3337,28 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Flobäcken, Flobäcken, Hjd</t>
@@ -3428,7 +3400,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3438,7 +3410,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3465,10 +3437,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119738011</v>
+        <v>119738082</v>
       </c>
       <c r="B26" t="n">
-        <v>79115</v>
+        <v>78262</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3481,21 +3453,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3505,13 +3477,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>417238</v>
+        <v>417270</v>
       </c>
       <c r="R26" t="n">
-        <v>6900663</v>
+        <v>6900698</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3540,7 +3512,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3550,7 +3522,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3565,22 +3537,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Liam Martin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann, Liam Martin</t>
+          <t>Liam Martin, Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119738442</v>
+        <v>119738570</v>
       </c>
       <c r="B27" t="n">
-        <v>79144</v>
+        <v>77910</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3593,21 +3565,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3652,7 +3624,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3662,7 +3634,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3689,10 +3661,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119738890</v>
+        <v>119738205</v>
       </c>
       <c r="B28" t="n">
-        <v>91852</v>
+        <v>77910</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3701,25 +3673,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4366</v>
+        <v>6437</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3729,13 +3701,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>417238</v>
+        <v>417270</v>
       </c>
       <c r="R28" t="n">
-        <v>6900663</v>
+        <v>6900698</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3764,7 +3736,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3774,7 +3746,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3789,12 +3761,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Liam Martin</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann, Liam Martin</t>
+          <t>Liam Martin, Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3913,10 +3885,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119739014</v>
+        <v>119738890</v>
       </c>
       <c r="B30" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3929,21 +3901,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3953,13 +3925,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>417270</v>
+        <v>417238</v>
       </c>
       <c r="R30" t="n">
-        <v>6900698</v>
+        <v>6900663</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3988,7 +3960,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3998,7 +3970,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4013,22 +3985,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Liam Martin</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Liam Martin, Alexander Hoffmann</t>
+          <t>Alexander Hoffmann, Liam Martin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119738570</v>
+        <v>119738239</v>
       </c>
       <c r="B31" t="n">
-        <v>77910</v>
+        <v>79144</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4041,21 +4013,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4065,13 +4037,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>417238</v>
+        <v>417270</v>
       </c>
       <c r="R31" t="n">
-        <v>6900663</v>
+        <v>6900698</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4100,7 +4072,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4110,7 +4082,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4125,19 +4097,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Liam Martin</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann, Liam Martin</t>
+          <t>Liam Martin, Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119738239</v>
+        <v>119739172</v>
       </c>
       <c r="B32" t="n">
         <v>79144</v>
@@ -4177,13 +4149,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>417270</v>
+        <v>417238</v>
       </c>
       <c r="R32" t="n">
-        <v>6900698</v>
+        <v>6900663</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4212,7 +4184,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4222,7 +4194,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4237,22 +4209,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Liam Martin</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Liam Martin, Alexander Hoffmann</t>
+          <t>Alexander Hoffmann, Liam Martin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119738933</v>
+        <v>119738266</v>
       </c>
       <c r="B33" t="n">
-        <v>91840</v>
+        <v>79115</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4261,41 +4233,50 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Flobäcken, Flobäcken, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>417238</v>
+        <v>417270</v>
       </c>
       <c r="R33" t="n">
-        <v>6900663</v>
+        <v>6900698</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4324,7 +4305,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4334,7 +4315,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4349,22 +4330,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Liam Martin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann, Liam Martin</t>
+          <t>Liam Martin, Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119738205</v>
+        <v>119738482</v>
       </c>
       <c r="B34" t="n">
-        <v>77910</v>
+        <v>57421</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4373,41 +4354,60 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6437</v>
+        <v>103031</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Flobäcken, Flobäcken, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>417270</v>
+        <v>417238</v>
       </c>
       <c r="R34" t="n">
-        <v>6900698</v>
+        <v>6900663</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4461,12 +4461,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Liam Martin</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Liam Martin, Alexander Hoffmann</t>
+          <t>Alexander Hoffmann, Liam Martin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>

--- a/artfynd/A 28811-2022 artfynd.xlsx
+++ b/artfynd/A 28811-2022 artfynd.xlsx
@@ -3885,10 +3885,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119738890</v>
+        <v>119738239</v>
       </c>
       <c r="B30" t="n">
-        <v>91852</v>
+        <v>79144</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3897,25 +3897,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4366</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3925,13 +3925,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>417238</v>
+        <v>417270</v>
       </c>
       <c r="R30" t="n">
-        <v>6900663</v>
+        <v>6900698</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3985,22 +3985,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Liam Martin</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann, Liam Martin</t>
+          <t>Liam Martin, Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119738239</v>
+        <v>119738890</v>
       </c>
       <c r="B31" t="n">
-        <v>79144</v>
+        <v>91852</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4009,25 +4009,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>4366</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4037,13 +4037,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>417270</v>
+        <v>417238</v>
       </c>
       <c r="R31" t="n">
-        <v>6900698</v>
+        <v>6900663</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4097,12 +4097,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Liam Martin</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Liam Martin, Alexander Hoffmann</t>
+          <t>Alexander Hoffmann, Liam Martin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>

--- a/artfynd/A 28811-2022 artfynd.xlsx
+++ b/artfynd/A 28811-2022 artfynd.xlsx
@@ -2989,10 +2989,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119738933</v>
+        <v>119738266</v>
       </c>
       <c r="B22" t="n">
-        <v>91840</v>
+        <v>79115</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3001,41 +3001,50 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Flobäcken, Flobäcken, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>417238</v>
+        <v>417270</v>
       </c>
       <c r="R22" t="n">
-        <v>6900663</v>
+        <v>6900698</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3064,7 +3073,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3074,7 +3083,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3089,22 +3098,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Liam Martin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann, Liam Martin</t>
+          <t>Liam Martin, Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119738721</v>
+        <v>119739172</v>
       </c>
       <c r="B23" t="n">
-        <v>78262</v>
+        <v>79144</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3117,21 +3126,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3176,7 +3185,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3186,7 +3195,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3213,10 +3222,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119738011</v>
+        <v>119738721</v>
       </c>
       <c r="B24" t="n">
-        <v>79115</v>
+        <v>78262</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3229,21 +3238,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3259,7 +3268,7 @@
         <v>6900663</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3288,7 +3297,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3298,7 +3307,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3325,10 +3334,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119739014</v>
+        <v>119738011</v>
       </c>
       <c r="B25" t="n">
-        <v>91840</v>
+        <v>79115</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3337,25 +3346,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3365,10 +3374,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>417270</v>
+        <v>417238</v>
       </c>
       <c r="R25" t="n">
-        <v>6900698</v>
+        <v>6900663</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3400,7 +3409,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3410,7 +3419,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3425,22 +3434,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Liam Martin</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Liam Martin, Alexander Hoffmann</t>
+          <t>Alexander Hoffmann, Liam Martin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119738082</v>
+        <v>119739089</v>
       </c>
       <c r="B26" t="n">
-        <v>78262</v>
+        <v>78171</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3453,21 +3462,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3477,10 +3486,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>417270</v>
+        <v>417238</v>
       </c>
       <c r="R26" t="n">
-        <v>6900698</v>
+        <v>6900663</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3512,7 +3521,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3522,7 +3531,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3537,12 +3546,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Liam Martin</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Liam Martin, Alexander Hoffmann</t>
+          <t>Alexander Hoffmann, Liam Martin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3661,10 +3670,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119738205</v>
+        <v>119739014</v>
       </c>
       <c r="B28" t="n">
-        <v>77910</v>
+        <v>91840</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3673,25 +3682,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3736,7 +3745,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3746,7 +3755,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3773,10 +3782,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119738232</v>
+        <v>119738890</v>
       </c>
       <c r="B29" t="n">
-        <v>78171</v>
+        <v>91852</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3785,25 +3794,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>353</v>
+        <v>4366</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3848,7 +3857,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3858,7 +3867,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3885,10 +3894,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119738239</v>
+        <v>119738082</v>
       </c>
       <c r="B30" t="n">
-        <v>79144</v>
+        <v>78262</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3901,21 +3910,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3931,7 +3940,7 @@
         <v>6900698</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3997,10 +4006,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119738890</v>
+        <v>119738205</v>
       </c>
       <c r="B31" t="n">
-        <v>91852</v>
+        <v>77910</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4009,25 +4018,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4366</v>
+        <v>6437</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4037,13 +4046,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>417238</v>
+        <v>417270</v>
       </c>
       <c r="R31" t="n">
-        <v>6900663</v>
+        <v>6900698</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4072,7 +4081,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4082,7 +4091,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4097,22 +4106,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Liam Martin</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann, Liam Martin</t>
+          <t>Liam Martin, Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119739172</v>
+        <v>119738933</v>
       </c>
       <c r="B32" t="n">
-        <v>79144</v>
+        <v>91840</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4121,25 +4130,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4184,7 +4193,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4194,7 +4203,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4221,10 +4230,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119738266</v>
+        <v>119738239</v>
       </c>
       <c r="B33" t="n">
-        <v>79115</v>
+        <v>79144</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4237,33 +4246,24 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Flobäcken, Flobäcken, Hjd</t>
@@ -4305,7 +4305,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4315,7 +4315,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 28811-2022 artfynd.xlsx
+++ b/artfynd/A 28811-2022 artfynd.xlsx
@@ -4230,10 +4230,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119738239</v>
+        <v>119738482</v>
       </c>
       <c r="B33" t="n">
-        <v>79144</v>
+        <v>57421</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4242,41 +4242,60 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>103031</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Flobäcken, Flobäcken, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>417270</v>
+        <v>417238</v>
       </c>
       <c r="R33" t="n">
-        <v>6900698</v>
+        <v>6900663</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4305,7 +4324,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4315,7 +4334,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4330,22 +4349,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Liam Martin</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Liam Martin, Alexander Hoffmann</t>
+          <t>Alexander Hoffmann, Liam Martin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119738482</v>
+        <v>119738239</v>
       </c>
       <c r="B34" t="n">
-        <v>57421</v>
+        <v>79144</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4354,60 +4373,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103031</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Flobäcken, Flobäcken, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>417238</v>
+        <v>417270</v>
       </c>
       <c r="R34" t="n">
-        <v>6900663</v>
+        <v>6900698</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4461,12 +4461,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Liam Martin</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann, Liam Martin</t>
+          <t>Liam Martin, Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>

--- a/artfynd/A 28811-2022 artfynd.xlsx
+++ b/artfynd/A 28811-2022 artfynd.xlsx
@@ -2989,10 +2989,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119738266</v>
+        <v>119738548</v>
       </c>
       <c r="B22" t="n">
-        <v>79115</v>
+        <v>91840</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3001,37 +3001,28 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Flobäcken, Flobäcken, Hjd</t>
@@ -3073,7 +3064,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3083,7 +3074,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3110,10 +3101,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119739172</v>
+        <v>119739081</v>
       </c>
       <c r="B23" t="n">
-        <v>79144</v>
+        <v>78262</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3126,21 +3117,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3185,7 +3176,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3195,7 +3186,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3222,10 +3213,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119738721</v>
+        <v>119738011</v>
       </c>
       <c r="B24" t="n">
-        <v>78262</v>
+        <v>79115</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3238,21 +3229,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3268,7 +3259,7 @@
         <v>6900663</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3297,7 +3288,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3307,7 +3298,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3334,7 +3325,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119738011</v>
+        <v>119738266</v>
       </c>
       <c r="B25" t="n">
         <v>79115</v>
@@ -3367,17 +3358,26 @@
           <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Flobäcken, Flobäcken, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>417238</v>
+        <v>417270</v>
       </c>
       <c r="R25" t="n">
-        <v>6900663</v>
+        <v>6900698</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3409,7 +3409,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3434,22 +3434,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Liam Martin</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann, Liam Martin</t>
+          <t>Liam Martin, Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119739089</v>
+        <v>119738205</v>
       </c>
       <c r="B26" t="n">
-        <v>78171</v>
+        <v>77910</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3462,21 +3462,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3486,13 +3486,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>417238</v>
+        <v>417270</v>
       </c>
       <c r="R26" t="n">
-        <v>6900663</v>
+        <v>6900698</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3546,12 +3546,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Liam Martin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann, Liam Martin</t>
+          <t>Liam Martin, Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3670,10 +3670,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119739014</v>
+        <v>119738232</v>
       </c>
       <c r="B28" t="n">
-        <v>91840</v>
+        <v>78171</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3682,25 +3682,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>417270</v>
+        <v>417238</v>
       </c>
       <c r="R28" t="n">
-        <v>6900698</v>
+        <v>6900663</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3770,22 +3770,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Liam Martin</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Liam Martin, Alexander Hoffmann</t>
+          <t>Alexander Hoffmann, Liam Martin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119738890</v>
+        <v>119738933</v>
       </c>
       <c r="B29" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3798,21 +3798,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3894,10 +3894,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119738082</v>
+        <v>119738442</v>
       </c>
       <c r="B30" t="n">
-        <v>78262</v>
+        <v>79144</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3910,21 +3910,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3934,10 +3934,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>417270</v>
+        <v>417238</v>
       </c>
       <c r="R30" t="n">
-        <v>6900698</v>
+        <v>6900663</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3969,7 +3969,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3994,22 +3994,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Liam Martin</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Liam Martin, Alexander Hoffmann</t>
+          <t>Alexander Hoffmann, Liam Martin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119738205</v>
+        <v>119738082</v>
       </c>
       <c r="B31" t="n">
-        <v>77910</v>
+        <v>78262</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4022,21 +4022,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4052,7 +4052,7 @@
         <v>6900698</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4118,10 +4118,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119738933</v>
+        <v>119738239</v>
       </c>
       <c r="B32" t="n">
-        <v>91840</v>
+        <v>79144</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4130,25 +4130,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4158,13 +4158,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>417238</v>
+        <v>417270</v>
       </c>
       <c r="R32" t="n">
-        <v>6900663</v>
+        <v>6900698</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4218,12 +4218,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Liam Martin</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann, Liam Martin</t>
+          <t>Liam Martin, Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4361,10 +4361,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119738239</v>
+        <v>119738890</v>
       </c>
       <c r="B34" t="n">
-        <v>79144</v>
+        <v>91852</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4373,25 +4373,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>4366</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4401,13 +4401,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>417270</v>
+        <v>417238</v>
       </c>
       <c r="R34" t="n">
-        <v>6900698</v>
+        <v>6900663</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4461,12 +4461,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Liam Martin</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Liam Martin, Alexander Hoffmann</t>
+          <t>Alexander Hoffmann, Liam Martin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>

--- a/artfynd/A 28811-2022 artfynd.xlsx
+++ b/artfynd/A 28811-2022 artfynd.xlsx
@@ -2989,10 +2989,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119738548</v>
+        <v>119738011</v>
       </c>
       <c r="B22" t="n">
-        <v>91840</v>
+        <v>79131</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3001,25 +3001,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3029,10 +3029,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>417270</v>
+        <v>417238</v>
       </c>
       <c r="R22" t="n">
-        <v>6900698</v>
+        <v>6900663</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3074,7 +3074,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3089,22 +3089,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Liam Martin</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Liam Martin, Alexander Hoffmann</t>
+          <t>Alexander Hoffmann, Liam Martin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119739081</v>
+        <v>119738082</v>
       </c>
       <c r="B23" t="n">
-        <v>78262</v>
+        <v>78278</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3141,10 +3141,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>417238</v>
+        <v>417270</v>
       </c>
       <c r="R23" t="n">
-        <v>6900663</v>
+        <v>6900698</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3201,22 +3201,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Liam Martin</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann, Liam Martin</t>
+          <t>Liam Martin, Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119738011</v>
+        <v>119738232</v>
       </c>
       <c r="B24" t="n">
-        <v>79115</v>
+        <v>78187</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3229,21 +3229,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3259,7 +3259,7 @@
         <v>6900663</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3325,10 +3325,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119738266</v>
+        <v>119738239</v>
       </c>
       <c r="B25" t="n">
-        <v>79115</v>
+        <v>79160</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3341,33 +3341,24 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Flobäcken, Flobäcken, Hjd</t>
@@ -3409,7 +3400,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3419,7 +3410,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3446,10 +3437,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119738205</v>
+        <v>119738144</v>
       </c>
       <c r="B26" t="n">
-        <v>77910</v>
+        <v>78278</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3462,21 +3453,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3486,13 +3477,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>417270</v>
+        <v>417238</v>
       </c>
       <c r="R26" t="n">
-        <v>6900698</v>
+        <v>6900663</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3521,7 +3512,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3531,7 +3522,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3546,22 +3537,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Liam Martin</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Liam Martin, Alexander Hoffmann</t>
+          <t>Alexander Hoffmann, Liam Martin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119738570</v>
+        <v>119739172</v>
       </c>
       <c r="B27" t="n">
-        <v>77910</v>
+        <v>79160</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3574,21 +3565,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3633,7 +3624,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3643,7 +3634,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3670,10 +3661,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119738232</v>
+        <v>119738570</v>
       </c>
       <c r="B28" t="n">
-        <v>78171</v>
+        <v>77926</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3686,21 +3677,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3745,7 +3736,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3755,7 +3746,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3785,7 +3776,7 @@
         <v>119738933</v>
       </c>
       <c r="B29" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3894,10 +3885,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119738442</v>
+        <v>119738548</v>
       </c>
       <c r="B30" t="n">
-        <v>79144</v>
+        <v>91858</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3906,25 +3897,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3934,13 +3925,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>417238</v>
+        <v>417270</v>
       </c>
       <c r="R30" t="n">
-        <v>6900663</v>
+        <v>6900698</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3969,7 +3960,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3979,7 +3970,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3994,22 +3985,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Liam Martin</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann, Liam Martin</t>
+          <t>Liam Martin, Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119738082</v>
+        <v>119738205</v>
       </c>
       <c r="B31" t="n">
-        <v>78262</v>
+        <v>77926</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4022,21 +4013,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4052,7 +4043,7 @@
         <v>6900698</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4118,10 +4109,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119738239</v>
+        <v>119738266</v>
       </c>
       <c r="B32" t="n">
-        <v>79144</v>
+        <v>79131</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4134,24 +4125,33 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Flobäcken, Flobäcken, Hjd</t>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4233,7 +4233,7 @@
         <v>119738482</v>
       </c>
       <c r="B33" t="n">
-        <v>57421</v>
+        <v>57431</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>119738890</v>
       </c>
       <c r="B34" t="n">
-        <v>91852</v>
+        <v>91870</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>

--- a/artfynd/A 28811-2022 artfynd.xlsx
+++ b/artfynd/A 28811-2022 artfynd.xlsx
@@ -3997,10 +3997,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119738205</v>
+        <v>119738266</v>
       </c>
       <c r="B31" t="n">
-        <v>77926</v>
+        <v>79131</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4013,24 +4013,33 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Flobäcken, Flobäcken, Hjd</t>
@@ -4072,7 +4081,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4082,7 +4091,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4109,10 +4118,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119738266</v>
+        <v>119738205</v>
       </c>
       <c r="B32" t="n">
-        <v>79131</v>
+        <v>77926</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4125,33 +4134,24 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Flobäcken, Flobäcken, Hjd</t>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4230,10 +4230,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119738482</v>
+        <v>119738890</v>
       </c>
       <c r="B33" t="n">
-        <v>57431</v>
+        <v>91870</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4246,43 +4246,24 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103031</v>
+        <v>4366</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Flobäcken, Flobäcken, Hjd</t>
@@ -4324,7 +4305,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4334,7 +4315,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4361,10 +4342,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119738890</v>
+        <v>119738482</v>
       </c>
       <c r="B34" t="n">
-        <v>91870</v>
+        <v>57431</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4377,24 +4358,43 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4366</v>
+        <v>103031</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Flobäcken, Flobäcken, Hjd</t>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD34" t="b">
